--- a/content.xlsx
+++ b/content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/WorkBuddy/2026-08-25-18-41-01/academic-homepage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67873747-F80F-6648-A36F-B175A670E6AB}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45826E98-2D07-024D-922B-98C919D186CF}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
   <si>
     <t>Key</t>
   </si>
@@ -117,10 +117,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Hi, I'm Qiao Huang. I am a linguistics researcher working on pragmatics, sociolinguistics, and philosophy and language.  My recent interests include doctor-patient communication, linguistic landscape, and varying types of discourse.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>[Huang, Q], [Y. Zhao]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -213,15 +209,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>https://scholar.google.com.hk/citations?user=6VZ_gTkAAAAJ&amp;hl=zh-CN</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ORCID</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://orcid.org/0000-0002-6435-5148</t>
+    <t>Hi, I'm Qiao Huang, an Associate Professor in the Department of English at Sichuan University. I work on pragmatics, sociolinguistics, and philosophy and language.  My recent interests include doctor-patient communication, linguistic landscape, and varying types of discourse.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -595,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -635,7 +623,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -658,9 +646,7 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>53</v>
-      </c>
+      <c r="B8" s="2"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
@@ -669,14 +655,6 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
@@ -684,8 +662,6 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B7" r:id="rId1" xr:uid="{EBE5C9AC-BB39-1A46-A173-09272D3A1B4D}"/>
-    <hyperlink ref="B8" r:id="rId2" xr:uid="{B25EA9CD-04CD-D243-A2AB-19626445DC95}"/>
-    <hyperlink ref="B10" r:id="rId3" xr:uid="{1A3F0F19-00C0-3E40-B88C-7B0ABC2A875E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -718,16 +694,16 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
         <v>30</v>
       </c>
-      <c r="D2" t="s">
-        <v>31</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -735,13 +711,13 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
         <v>34</v>
-      </c>
-      <c r="D3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -749,16 +725,16 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
         <v>37</v>
       </c>
-      <c r="C4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -766,16 +742,16 @@
         <v>2023</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" t="s">
         <v>42</v>
       </c>
-      <c r="D5" t="s">
-        <v>43</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -783,13 +759,13 @@
         <v>2021</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -821,26 +797,26 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" t="s">
         <v>51</v>
-      </c>
-      <c r="B2" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" t="s">
         <v>49</v>
-      </c>
-      <c r="B3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s">
         <v>47</v>
-      </c>
-      <c r="B4" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/content.xlsx
+++ b/content.xlsx
@@ -8,22 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/WorkBuddy/2026-08-25-18-41-01/academic-homepage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45826E98-2D07-024D-922B-98C919D186CF}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA74AF55-34B1-1F44-9F40-5550EDAC72C2}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="1" r:id="rId1"/>
-    <sheet name="Publications" sheetId="2" r:id="rId2"/>
-    <sheet name="Research" sheetId="3" r:id="rId3"/>
-    <sheet name="News" sheetId="4" r:id="rId4"/>
+    <sheet name="Research" sheetId="3" r:id="rId2"/>
+    <sheet name="Books" sheetId="7" r:id="rId3"/>
+    <sheet name="Journal Articles" sheetId="2" r:id="rId4"/>
+    <sheet name="Projects" sheetId="5" r:id="rId5"/>
+    <sheet name="News" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
   <si>
     <t>Key</t>
   </si>
@@ -55,6 +57,9 @@
     <t>github</t>
   </si>
   <si>
+    <t>linkedin</t>
+  </si>
+  <si>
     <t>cv</t>
   </si>
   <si>
@@ -97,18 +102,22 @@
     <t>Launched my academic homepage.</t>
   </si>
   <si>
+    <t>Ph.D.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>Qiao Huang</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Associate Professor</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Sichuan University</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Hi, I'm Qiao Huang, an Associate Professor in the Department of English at Sichuan University. I work on pragmatics, sociolinguistics, and philosophy and language. My recent interests include doctor-patient communication, linguistic landscape, and varying types of discourse.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>photo.jpg</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -117,7 +126,42 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>[Huang, Q], [Y. Zhao]</t>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Year</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Discourse Analysis</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Investigating the forms and functions of varying types of discourse.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Linguistic Landscape</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exploring the language use on public signs and its relationship with authenticity, identity, among others.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Semantic Minimalism</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Defending a position advocating that the meaning of linguistic expressions is largely free from context.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A gradient of compliance: Language policy, local identity, and the linguistic landscape of Chengdu's restaurant shop signs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Huang, Q. &amp; Y. Zhao</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -129,11 +173,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> A gradient of compliance: Language policy, local identity, and the linguistic landscape of Chengdu's restaurant shop signs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[黄乔], [张玥]</t>
+    <t>黄乔, 张玥</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -141,11 +181,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>[Huang, Q]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> The state of the field report Ⅻ: Contemporary Chinese studies of the philosophy of language in the Gongsun Longzi</t>
+    <t>The state of the field report Ⅻ: Contemporary Chinese studies of the philosophy of language in the Gongsun Longzi</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Huang, Q</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -153,19 +193,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>https://doi.org/10.1007/s11712-024-09935-w</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://doi.org/10.1080/01434632.2025.2598020</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://doi.org/10.13978/j.cnki.wyyj.2023.05.001</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[黄乔], [刘利民]</t>
+    <t>语义最小论视阈下的语词意义再议</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄乔, 刘利民</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>语义最小论与语境论之争再探——从语境的角度看</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -177,39 +213,27 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 语义最小论视阈下的语词意义再议</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 语义最小论与语境论之争再探——从语境的角度看</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Semantic Minimalism</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Defending a position advocating that the meaning of linguistic expressions is largely free from the influence of context. </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Linguistic Landscape</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Exploring the language use on public signs and its relationship with authenticity, identity, among others.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Discourse Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Investigating the forms and functions of varying types of discourse.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hi, I'm Qiao Huang, an Associate Professor in the Department of English at Sichuan University. I work on pragmatics, sociolinguistics, and philosophy and language.  My recent interests include doctor-patient communication, linguistic landscape, and varying types of discourse.</t>
+    <t>博格语义最小论研究</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄乔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>社会科学文献出版社</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>省部级</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Publisher</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -230,6 +254,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -583,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -599,7 +624,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -615,7 +640,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -623,7 +648,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -631,7 +656,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -639,14 +664,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="2"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
@@ -658,35 +682,128 @@
         <v>10</v>
       </c>
     </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{EBE5C9AC-BB39-1A46-A173-09272D3A1B4D}"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{9C6B4698-FA69-2041-87DE-9E7816127984}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FED6F81-58E6-744C-BA8D-8DFB66121165}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>2026</v>
+      </c>
+      <c r="B2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -694,47 +811,41 @@
         <v>2025</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -742,16 +853,13 @@
         <v>2023</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -759,64 +867,13 @@
         <v>2021</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="E4" r:id="rId1" xr:uid="{39F23DAA-6494-C049-89CF-0282C0EB51CA}"/>
-    <hyperlink ref="E2" r:id="rId2" xr:uid="{B1AC7271-8FEC-4A4F-846F-79B40B2F10D4}"/>
-    <hyperlink ref="E5" r:id="rId3" xr:uid="{7CEE9326-8471-9948-87FA-CDC08A89671A}"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -825,25 +882,58 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>2025</v>
+      </c>
+      <c r="B2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/content.xlsx
+++ b/content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/WorkBuddy/2026-08-25-18-41-01/academic-homepage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA74AF55-34B1-1F44-9F40-5550EDAC72C2}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{111578A9-8FCA-1940-899B-50631BF5DD53}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="1" r:id="rId1"/>

--- a/content.xlsx
+++ b/content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/WorkBuddy/2026-08-25-18-41-01/academic-homepage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{111578A9-8FCA-1940-899B-50631BF5DD53}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2F05E9-0706-AC41-A158-09DE22F024F3}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
   <si>
     <t>Key</t>
   </si>
@@ -222,14 +222,6 @@
   </si>
   <si>
     <t>社会科学文献出版社</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Level</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>省部级</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -758,7 +750,7 @@
         <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>16</v>
@@ -894,9 +886,7 @@
       <c r="B1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>56</v>
-      </c>
+      <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
@@ -904,9 +894,6 @@
       </c>
       <c r="B2" t="s">
         <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
